--- a/車両マスター.xlsx
+++ b/車両マスター.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>車両ID</t>
   </si>
@@ -92,10 +92,19 @@
     <t>2024/09/27 11:17:08</t>
   </si>
   <si>
-    <t>2024/10/01 12:44:09</t>
+    <t>2024/10/01 15:19:11</t>
   </si>
   <si>
     <t>澤井 宏佑</t>
+  </si>
+  <si>
+    <t>4444</t>
+  </si>
+  <si>
+    <t>7777</t>
+  </si>
+  <si>
+    <t>2024/10/02 15:44:19</t>
   </si>
 </sst>
 </file>
@@ -142,7 +151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -325,6 +334,32 @@
       </c>
       <c r="H7" s="0" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>27</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
